--- a/outputs/results/phase5_dl_prediction_results.xlsx
+++ b/outputs/results/phase5_dl_prediction_results.xlsx
@@ -448,10 +448,10 @@
         <v>0.4129999876022339</v>
       </c>
       <c r="C2" t="n">
-        <v>1.280269980430603</v>
+        <v>1.280269861221313</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8672699928283691</v>
+        <v>0.8672698736190796</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>0.4129999876022339</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1087436452507973</v>
+        <v>0.1087436899542809</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3042563423514366</v>
+        <v>0.304256297647953</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0.4129999876022339</v>
       </c>
       <c r="C4" t="n">
-        <v>1.576996803283691</v>
+        <v>1.57699716091156</v>
       </c>
       <c r="D4" t="n">
-        <v>1.163996815681458</v>
+        <v>1.163997173309326</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>0.4129999876022339</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5535358786582947</v>
+        <v>0.5535358190536499</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1405358910560608</v>
+        <v>0.140535831451416</v>
       </c>
     </row>
     <row r="6">
@@ -560,10 +560,10 @@
         <v>0.5609999895095825</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5218008160591125</v>
+        <v>0.5218007564544678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03919917345046997</v>
+        <v>0.03919923305511475</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         <v>0.8209999799728394</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5260297656059265</v>
+        <v>0.5260297060012817</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2949702143669128</v>
+        <v>0.2949702739715576</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         <v>0.8169999718666077</v>
       </c>
       <c r="C11" t="n">
-        <v>3.325416803359985</v>
+        <v>3.325417041778564</v>
       </c>
       <c r="D11" t="n">
-        <v>2.508416831493378</v>
+        <v>2.508417069911957</v>
       </c>
     </row>
     <row r="12">
@@ -640,10 +640,10 @@
         <v>0.1410000026226044</v>
       </c>
       <c r="C14" t="n">
-        <v>0.746275007724762</v>
+        <v>0.7462750673294067</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6052750051021576</v>
+        <v>0.6052750647068024</v>
       </c>
     </row>
     <row r="15">
@@ -656,10 +656,10 @@
         <v>0.3880000114440918</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1964219510555267</v>
+        <v>0.1964219808578491</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1915780603885651</v>
+        <v>0.1915780305862427</v>
       </c>
     </row>
     <row r="16">
@@ -720,10 +720,10 @@
         <v>0.4289999902248383</v>
       </c>
       <c r="C19" t="n">
-        <v>2.506803274154663</v>
+        <v>2.506803512573242</v>
       </c>
       <c r="D19" t="n">
-        <v>2.077803283929825</v>
+        <v>2.077803522348404</v>
       </c>
     </row>
     <row r="20">
@@ -736,10 +736,10 @@
         <v>1.791000008583069</v>
       </c>
       <c r="C20" t="n">
-        <v>1.674606800079346</v>
+        <v>1.674606442451477</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1163932085037231</v>
+        <v>0.1163935661315918</v>
       </c>
     </row>
     <row r="21">
